--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5601-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5601-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19137756-CC25-470F-862A-C2026A8DCDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29CA8D03-FFF6-4A96-AE55-9C3B9572ADAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8D9DB7B9-5D09-4D87-8DC5-A77D051521B5}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F187F92F-452F-4A0A-8C6F-C4EEE26B2575}"/>
   </bookViews>
   <sheets>
     <sheet name="5601-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1583,29 +1583,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E5AF21A-88AD-412A-B678-D119BD745499}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8655EAD5-B122-4A49-8F73-47A743DD4E2A}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1639,7 +1638,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1675,7 +1674,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1727,7 +1726,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1795,7 +1794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1867,7 +1866,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1939,7 +1938,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2011,7 +2010,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2083,7 +2082,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2227,7 +2226,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2299,7 +2298,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2371,7 +2370,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2443,7 +2442,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2515,7 +2514,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2587,7 +2586,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2659,7 +2658,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2731,7 +2730,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2803,7 +2802,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2875,7 +2874,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2947,7 +2946,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -3019,7 +3018,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3091,7 +3090,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>2006</v>
       </c>
@@ -3163,7 +3162,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2005</v>
       </c>
@@ -3235,7 +3234,7 @@
         <v>5.86</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2004</v>
       </c>
@@ -3307,7 +3306,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2003</v>
       </c>
@@ -3379,7 +3378,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2002</v>
       </c>
@@ -3451,7 +3450,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="39">
         <v>2001</v>
       </c>
@@ -3523,7 +3522,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2000</v>
       </c>
@@ -3595,7 +3594,7 @@
         <v>8.93</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>1999</v>
       </c>
@@ -3667,7 +3666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1998</v>
       </c>
@@ -3739,7 +3738,7 @@
         <v>13.4</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="39">
         <v>1997</v>
       </c>
@@ -3811,7 +3810,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="41">
         <v>1996</v>
       </c>
@@ -3883,7 +3882,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="43"/>
       <c r="B34" s="44"/>
       <c r="C34" s="18" t="s">
@@ -3911,7 +3910,7 @@
       <c r="W34" s="50"/>
       <c r="X34" s="46"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1995</v>
       </c>
@@ -3983,7 +3982,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="41">
         <v>1994</v>
       </c>
@@ -4055,7 +4054,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="43"/>
       <c r="B37" s="44"/>
       <c r="C37" s="18" t="s">
@@ -4083,7 +4082,7 @@
       <c r="W37" s="50"/>
       <c r="X37" s="46"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="51">
         <v>1993</v>
       </c>
@@ -4155,7 +4154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="53"/>
       <c r="B39" s="54"/>
       <c r="C39" s="20" t="s">
@@ -4183,7 +4182,7 @@
       <c r="W39" s="60"/>
       <c r="X39" s="56"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="41">
         <v>1992</v>
       </c>
@@ -4255,7 +4254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="43"/>
       <c r="B41" s="44"/>
       <c r="C41" s="18" t="s">
@@ -4283,7 +4282,7 @@
       <c r="W41" s="50"/>
       <c r="X41" s="46"/>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="39" t="s">
         <v>63</v>
       </c>
